--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="359">
   <si>
     <t>S.No.</t>
   </si>
@@ -514,10 +514,11 @@
 2. Look for the Load more ... control.</t>
   </si>
   <si>
-    <t>Load more ... is removed from the page, not merely disabled. An automated check must assert absence, not a disabled state.</t>
-  </si>
-  <si>
-    <t>Verified live 2026-08-24. Same behaviour as the Classes and Students tabs.</t>
+    <t xml:space="preserve">Each click appends the next page of 20 (the last click appending only what remains). Once the whole list is loaded, "Load more ..." is removed from the page, not merely disabled. An automated check must assert absence, not a disabled state.
+The number of clicks required is ceil(N / 20) - 1, where N is the heading count "Staff (N)": e.g. 23 staff = 1 click, 80 = 3 clicks, 85 = 4 clicks. A list of exactly 20 or fewer never shows the link at all (covered by TST_STFL_TC_25).</t>
+  </si>
+  <si>
+    <t>Verified live 2026-08-24. Same behaviour as the Classes and Students tabs. Click count added 2026-08-26 so the loop is predictable per school - the step already said "repeatedly", but gave no way to know how many clicks to expect. Note: FCN-CHZ-PDA held 23 staff at capture, so ONE click exhausted the list; a single-click implementation would pass there and break as soon as the school exceeds 40. Loop until the link disappears, never a fixed count. See also TST_STFL_TC_26 - on this tab the rendered row count does NOT match the heading count (a known defect), so do NOT use the heading total as the loop-termination condition; terminate on the link being gone.</t>
   </si>
   <si>
     <t>TST_STFL_TC_25</t>
@@ -547,10 +548,20 @@
 4. Compare the two numbers.</t>
   </si>
   <si>
-    <t>Expected: the number of rendered rows equals the heading count. Actual (verified live 2026-08-24): the heading read Staff (23) but the exhausted list rendered only 21 unique rows — a shortfall of 2 with Load more ... already removed.</t>
+    <t xml:space="preserve">The number of rendered rows EQUALS the heading count "Staff (N)" once "Load more ..." has been removed.
+This is the correct expectation and it MUST NOT be relaxed. The product currently fails it - see Actual Result.</t>
   </si>
   <si>
     <t>Expected-versus-actual — a real defect, confirmed with the team 2026-08-24. The count is NOT explained by pending invitations: the team confirmed that Staff (N) increments only when an invited teacher ACCEPTS, so invited-but-not-joined staff are not counted. The 2-row shortfall is therefore unexplained. It may be specific to this school's data. Because the school is shared, automate this as "heading count equals rendered row count", never as the literal numbers 23 and 21 — and expect this case to FAIL on FCN-CHZ-PDA until the data or the defect is fixed.</t>
+  </si>
+  <si>
+    <t>FAILS (verified live 2026-08-24). The heading read "Staff (23)" but the exhausted list rendered only 21 unique rows - a shortfall of 2, with "Load more ..." already removed.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>&lt;DEFECT_ID - to be raised&gt;. This case is a defect guard: the automated test is EXPECTED TO FAIL until the product is fixed. Automate the assertion as "rendered row count === heading count" and leave it failing. Do NOT weaken it to the observed numbers (23/21), do NOT assert "rows &lt;= heading", and do NOT skip, quarantine or .skip() it to get a green suite - that would delete the only signal that this defect exists. When the suite is red on this case alone, that is the correct state. Discussed with the team 2026-08-24; the cause is still unexplained.</t>
   </si>
   <si>
     <t>TST_STFL_TC_27</t>
@@ -2723,13 +2734,13 @@
         <v>166</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>24</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2737,13 +2748,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>17</v>
@@ -2752,19 +2763,19 @@
         <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
@@ -2781,13 +2792,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2799,16 +2810,16 @@
         <v>19</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
@@ -2825,13 +2836,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2843,13 +2854,13 @@
         <v>19</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>130</v>
@@ -2869,13 +2880,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>17</v>
@@ -2884,19 +2895,19 @@
         <v>18</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
@@ -2913,13 +2924,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>35</v>
@@ -2931,16 +2942,16 @@
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
@@ -2957,13 +2968,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>87</v>
@@ -2975,16 +2986,16 @@
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>24</v>
@@ -2993,7 +3004,7 @@
         <v>25</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -3001,13 +3012,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>17</v>
@@ -3019,16 +3030,16 @@
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
@@ -3045,13 +3056,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>35</v>
@@ -3063,16 +3074,16 @@
         <v>19</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -3089,13 +3100,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>17</v>
@@ -3104,19 +3115,19 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
@@ -3133,13 +3144,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3148,19 +3159,19 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
@@ -3177,13 +3188,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>17</v>
@@ -3192,16 +3203,16 @@
         <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>130</v>
@@ -3221,13 +3232,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>17</v>
@@ -3236,19 +3247,19 @@
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
@@ -3265,13 +3276,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>17</v>
@@ -3280,19 +3291,19 @@
         <v>18</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
@@ -3309,13 +3320,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>35</v>
@@ -3324,19 +3335,19 @@
         <v>36</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
@@ -3353,13 +3364,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>17</v>
@@ -3368,19 +3379,19 @@
         <v>18</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
@@ -3397,13 +3408,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>17</v>
@@ -3412,19 +3423,19 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
@@ -3441,13 +3452,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>17</v>
@@ -3456,19 +3467,19 @@
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
@@ -3485,13 +3496,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>35</v>
@@ -3500,19 +3511,19 @@
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
@@ -3529,13 +3540,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>17</v>
@@ -3547,16 +3558,16 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>24</v>
@@ -3573,13 +3584,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>17</v>
@@ -3588,19 +3599,19 @@
         <v>18</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
@@ -3617,13 +3628,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>17</v>
@@ -3632,19 +3643,19 @@
         <v>36</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
@@ -3661,13 +3672,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>17</v>
@@ -3676,19 +3687,19 @@
         <v>36</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>24</v>
@@ -3705,13 +3716,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -3720,19 +3731,19 @@
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
@@ -3749,13 +3760,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>35</v>
@@ -3764,19 +3775,19 @@
         <v>36</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
@@ -3793,13 +3804,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>35</v>
@@ -3808,19 +3819,19 @@
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
@@ -3837,13 +3848,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>35</v>
@@ -3852,19 +3863,19 @@
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
@@ -3881,13 +3892,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>35</v>
@@ -3896,19 +3907,19 @@
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
@@ -3925,13 +3936,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>87</v>
@@ -3940,19 +3951,19 @@
         <v>18</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
@@ -3969,13 +3980,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>87</v>
@@ -3984,28 +3995,28 @@
         <v>18</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4013,13 +4024,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>87</v>
@@ -4031,16 +4042,16 @@
         <v>19</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="373">
   <si>
     <t>S.No.</t>
   </si>
@@ -84,7 +84,7 @@
     <t>The URL is /admin/admin/org_&lt;slug&gt;/staff and the browser tab reads "Staff | Cambridge One". The page shows: heading Staff (N); a search box placeholder Search by first name, last name or email with a Search button; a Manage staff menu; a collapsed User guide toggle; a sortable table headed Last name | First name | Email address | Role, sorted by Last name ascending; up to 20 staff rows; and Load more ... when more than 20 staff exist.</t>
   </si>
   <si>
-    <t>Column set differs from the Students tab — there is a Role column and there is NO row-selection checkbox, no N Selected counter and no bulk "Remove from school account" on the list. Role values seen: Teacher, Administrator/Teacher.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Column set differs from the Students tab — there is a Role column and there is NO row-selection checkbox, no N Selected counter and no bulk "Remove from school account" on the list. Role values seen: Teacher, Administrator/Teacher.</t>
   </si>
   <si>
     <t/>
@@ -179,7 +179,7 @@
     <t>The list is not filtered — the heading still reads Staff (N) and the same rows are shown. Search is submit-driven, not live.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24: typing alone left the heading at Staff (23).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24: typing alone left the heading at Staff (23).</t>
   </si>
   <si>
     <t>TST_STFL_TC_6</t>
@@ -220,7 +220,7 @@
     <t>The banner is replaced by the Staff (N) count heading, the search box is emptied, the first page of 20 staff is shown again and Load more ... reappears.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24: heading returned to Staff (23), box empty, 20 rows, Load more present.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24: heading returned to Staff (23), box empty, 20 rows, Load more present.</t>
   </si>
   <si>
     <t>TST_STFL_TC_8</t>
@@ -280,7 +280,7 @@
     <t>The term is trimmed to nothing, but the page still enters the search banner state — the count heading is replaced by Showing search results for . with Clear — and every staff member is returned. [ASSUMED] — not exercised live on the Staff tab; this is the confirmed Students-tab behaviour.</t>
   </si>
   <si>
-    <t>[ASSUMED]. Entering the banner state on an empty term is arguably wrong; it is recorded as an observation, not a defect case. Confirm during Phase 1.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. [ASSUMED]. Entering the banner state on an empty term is arguably wrong; it is recorded as an observation, not a defect case. Confirm during Phase 1.</t>
   </si>
   <si>
     <t>TST_STFL_TC_11</t>
@@ -478,7 +478,7 @@
     <t>The list is truncated back to the first 20 rows in the new order and Load more ... is present again.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 — sorting resets pagination.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — sorting resets pagination.</t>
   </si>
   <si>
     <t>TST_STFL_TC_23</t>
@@ -550,7 +550,7 @@
     <t>Expected: the number of rendered rows equals the heading count. Actual (verified live 2026-08-24): the heading read Staff (23) but the exhausted list rendered only 21 unique rows — a shortfall of 2 with Load more ... already removed.</t>
   </si>
   <si>
-    <t>Expected-versus-actual — a real defect, confirmed with the team 2026-08-24. The count is NOT explained by pending invitations: the team confirmed that Staff (N) increments only when an invited teacher ACCEPTS, so invited-but-not-joined staff are not counted. The 2-row shortfall is therefore unexplained. It may be specific to this school's data. Because the school is shared, automate this as "heading count equals rendered row count", never as the literal numbers 23 and 21 — and expect this case to FAIL on FCN-CHZ-PDA until the data or the defect is fixed.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual — a real defect, confirmed with the team 2026-08-24. The count is NOT explained by pending invitations: the team confirmed that Staff (N) increments only when an invited teacher ACCEPTS, so invited-but-not-joined staff are not counted. The 2-row shortfall is therefore unexplained. It may be specific to this school's data. Because the school is shared, automate this as "heading count equals rendered row count", never as the literal numbers 23 and 21 — and expect this case to FAIL on FCN-CHZ-PDA until the data or the defect is fixed.</t>
   </si>
   <si>
     <t>TST_STFL_TC_27</t>
@@ -636,7 +636,7 @@
     <t>The Staff tab is shown again at /admin/admin/org_&lt;slug&gt;/staff, in its default state — heading Staff (N), sorted by Last name ascending, first page of 20 rows.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24. Any search or sort applied before opening the profile is NOT preserved on return — check this explicitly during Phase 1 if a test depends on it.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Any search or sort applied before opening the profile is NOT preserved on return — check this explicitly during Phase 1 if a test depends on it.</t>
   </si>
   <si>
     <t>TST_STFP_TC_4</t>
@@ -655,7 +655,7 @@
     <t>The classes section shows No class with Your classes will appear here and an Add classes control, instead of a Classes (N) list.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 on two separate profiles. [ASSUMED] that teacher17aug2026@mailsac.com also has no classes — confirm on the first run and swap the fixture if it does.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 on two separate profiles. [ASSUMED] that teacher17aug2026@mailsac.com also has no classes — confirm on the first run and swap the fixture if it does.</t>
   </si>
   <si>
     <t>TST_STFP_TC_6</t>
@@ -677,7 +677,7 @@
     <t>Expected: the user sees an error explaining that the profile could not be loaded, and the Staff list remains usable — a different row can still be opened. Actual (verified live 2026-08-24): nothing is shown at all, the app silently stays on the list, and the #loader-container overlay is left visible so every subsequent row click is intercepted until the page is reloaded.</t>
   </si>
   <si>
-    <t>Expected-versus-actual, scoped to CLIENT-SIDE ERROR HANDLING only. The underlying HTTP 500 from getUserDetailWithClasses is a KNOWN DATA ISSUE on this one account — confirmed with the team 2026-08-24 — and is NOT part of this case; do not raise it as a product defect. What remains product-side is that any 500 produces no message and a stuck overlay. The 500 account is retained deliberately as the trigger fixture; teacher17aug2026@mailsac.com is the healthy teacher fixture used elsewhere.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual, scoped to CLIENT-SIDE ERROR HANDLING only. The underlying HTTP 500 from getUserDetailWithClasses is a KNOWN DATA ISSUE on this one account — confirmed with the team 2026-08-24 — and is NOT part of this case; do not raise it as a product defect. What remains product-side is that any 500 produces no message and a stuck overlay. The 500 account is retained deliberately as the trigger fixture; teacher17aug2026@mailsac.com is the healthy teacher fixture used elsewhere.</t>
   </si>
   <si>
     <t>HTTP 500 confirmed as a known data issue with the team, 2026-08-24. Case narrowed to the missing error handling and the stuck loading overlay.</t>
@@ -722,7 +722,7 @@
     <t>The heading reads Classes (N) and each entry shows the class name, its date range, Date joined: &lt;date&gt;, Class key: &lt;key&gt; and the course material name — e.g. A11y test / Jul 11, 2025 - Jul 10, 2026 / Date joined: Jul 11, 2025 / Class key: iCmL-9Y8J / Collaborate 3 (NLP).</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24. Launching an ended class shows the class page with the banner As this class ended over a month ago, you can no longer reactivate it. and a Class ended status.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Launching an ended class shows the class page with the banner As this class ended over a month ago, you can no longer reactivate it. and a Class ended status.</t>
   </si>
   <si>
     <t>TST_STFP_TC_9</t>
@@ -855,7 +855,7 @@
     <t>Remove admin rights and Remove from school account are both offered on the administrator's own profile — the product does not exclude the signed-in user from either action.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 (menu inspected only). Never confirm either action on this account — it is the login used by every admin suite, and self-revoking would lock the whole programme out. Worth raising: should self-revocation and self-removal be prevented, or at least warned about?</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 (menu inspected only). Never confirm either action on this account — it is the login used by every admin suite, and self-revoking would lock the whole programme out. Worth raising: should self-revocation and self-removal be prevented, or at least warned about?</t>
   </si>
   <si>
     <t>TST_STFP_TC_15</t>
@@ -1055,7 +1055,7 @@
     <t>All three bulk actions are presented as unavailable while 0 Selected is shown.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24. Automation trap: these three controls carry no qid and are disabled by the CSS class disable (not disabled, and with no native disabled property). Resolve them by their text and assert on the class.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Automation trap: these three controls carry no qid and are disabled by the CSS class disable (not disabled, and with no native disabled property). Resolve them by their text and assert on the class.</t>
   </si>
   <si>
     <t>TST_STFB_TC_6</t>
@@ -1074,7 +1074,7 @@
     <t>The form is not empty — the previously entered rows are restored, a Saved &lt;age&gt; indicator is shown (e.g. Saved 30+ days ago), the submit button counts the restored rows, and any validation messages on those rows are already displayed.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 — the form opened showing Saved 30+ days ago, four restored rows and live validation messages. Same auto-save/restore behaviour as the Create new classes form (admin-shared.md §A4). A test that assumes an empty form will fail, and the draft is shared state on a shared school — do not assume your own suite wrote it.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — the form opened showing Saved 30+ days ago, four restored rows and live validation messages. Same auto-save/restore behaviour as the Create new classes form (admin-shared.md §A4). A test that assumes an empty form will fail, and the draft is shared state on a shared school — do not assume your own suite wrote it.</t>
   </si>
   <si>
     <t>TST_STFB_TC_7</t>
@@ -1093,7 +1093,7 @@
     <t>The Send N invites button is unavailable while any row fails validation.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 — the button was both natively disabled and carried the disabled class in this state.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — the button was both natively disabled and carried the disabled class in this state.</t>
   </si>
   <si>
     <t>TST_STFB_TC_9</t>
@@ -1138,7 +1138,7 @@
     <t>The messages are shown verbatim: Select student or teacher under an empty Role, Enter a valid class key under an invalid Class key, and Add a teacher’s email under an empty Email on a teacher row.</t>
   </si>
   <si>
-    <t>All three captured verbatim live 2026-08-24 from a restored draft. Add a teacher’s email confirms the form does distinguish the teacher case even though its help copy does not.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. All three captured verbatim live 2026-08-24 from a restored draft. Add a teacher’s email confirms the form does distinguish the teacher case even though its help copy does not.</t>
   </si>
   <si>
     <t>TST_STFB_TC_11</t>
@@ -1154,7 +1154,7 @@
     <t>Expected: the dialog reads Form not uploaded / An unexpected error occured. Please try again. / Close — the strings the product already ships. Actual (verified in the pre-rendered DOM, 2026-08-24): it renders three raw translation keys — ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_HEADING as the heading, ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_INFO as the body and ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_CLOSE as the close button.</t>
   </si>
   <si>
-    <t>Expected-versus-actual. ROOT CAUSE established from the admin bundle 2026-08-24: the modal is #existingChildFormUploadErrorModal, a component reused from the add-existing-children CSV flow, but on this page it looks its copy up under ADMIN.LEARNER.ADULT_INVITE. The FORM_UPLOAD_ERROR_* strings are defined ONLY under ADMIN.LEARNER.EXISTING_CHILD and ADMIN.LEARNER.BULK_ACTIVATION (in both en and es) — the ADULT_INVITE block exists but does not define them, so ngx-translate falls back to printing the key. Changing site language does not help; Spanish has the same gap. Control test: the same dialog on the add-existing-children CSV screen renders correctly, which is why this has gone unnoticed. Note the correct string carries the known occured typo already recorded in admin-students-tab.md. Found by free-capture of the pre-rendered DOM (admin-shared.md A6) before the state was ever reached.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual. ROOT CAUSE established from the admin bundle 2026-08-24: the modal is #existingChildFormUploadErrorModal, a component reused from the add-existing-children CSV flow, but on this page it looks its copy up under ADMIN.LEARNER.ADULT_INVITE. The FORM_UPLOAD_ERROR_* strings are defined ONLY under ADMIN.LEARNER.EXISTING_CHILD and ADMIN.LEARNER.BULK_ACTIVATION (in both en and es) — the ADULT_INVITE block exists but does not define them, so ngx-translate falls back to printing the key. Changing site language does not help; Spanish has the same gap. Control test: the same dialog on the add-existing-children CSV screen renders correctly, which is why this has gone unnoticed. Note the correct string carries the known occured typo already recorded in admin-students-tab.md. Found by free-capture of the pre-rendered DOM (admin-shared.md A6) before the state was ever reached.</t>
   </si>
   <si>
     <t>Blocked</t>
@@ -1176,7 +1176,58 @@
     <t>Expected: a title naming staff or the invitation form. Actual (verified live 2026-08-24): the tab reads Students | Cambridge One, even though the page was reached from the Staff tab and is headed Invite students and teachers.</t>
   </si>
   <si>
-    <t>Expected-versus-actual, low severity. Consistent with TST_STFB_TC_4 — the shared invite form is presented as a students screen throughout. Group both with the product owner as one copy/labelling issue rather than two.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual, low severity. Consistent with TST_STFB_TC_4 — the shared invite form is presented as a students screen throughout. Group both with the product owner as one copy/labelling issue rather than two.</t>
+  </si>
+  <si>
+    <t>TST_STFP_TC_19</t>
+  </si>
+  <si>
+    <t>Verify a newly promoted administrator can actually open the admin console</t>
+  </si>
+  <si>
+    <t>#9 - Verify Grant admin rights</t>
+  </si>
+  <si>
+    <t>A disposable teacher account exists whose password the tester controls, currently without admin rights.</t>
+  </si>
+  <si>
+    <t>1. As an administrator, open the teacher's staff profile &gt; Manage account &gt; Grant admin rights and confirm. 2. Verify the role now reads Administrator/Teacher. 3. Sign out. 4. Sign in as that user. 5. Open the school and confirm the admin console and its tabs are reachable.</t>
+  </si>
+  <si>
+    <t>Disposable teacher &lt;DISPOSABLE_STAFF_ACCOUNT&gt; on the target school.</t>
+  </si>
+  <si>
+    <t>After the grant, the user can sign in and reach the admin console for that school, seeing the administrator tabs. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STF_009, whose step 3 is "log in as that user and confirm admin console access". Our TST_STFP_TC_10 stops at the role label changing in the UI - which a grant that updated the display but not the permission would also satisfy. This is the same shape as the Students password gap (TST_SPRF_TC_23): we verify the UI acknowledged the change, not that the change took effect. Mutates a real account - data-mutating suite, and revoke the rights afterwards as housekeeping.</t>
+  </si>
+  <si>
+    <t>TST_STFP_TC_20</t>
+  </si>
+  <si>
+    <t>Verify admin rights cannot be revoked from the only remaining administrator</t>
+  </si>
+  <si>
+    <t>#11 - Verify revoke admin rights</t>
+  </si>
+  <si>
+    <t>A school whose staff list contains exactly one administrator.</t>
+  </si>
+  <si>
+    <t>1. Open the sole administrator's staff profile &gt; Manage account. 2. Attempt Remove admin rights. 3. Read whether the control is unavailable or the action is blocked, and the message shown. 4. Re-read the role afterwards.</t>
+  </si>
+  <si>
+    <t>A school with a single administrator.</t>
+  </si>
+  <si>
+    <t>The action is prevented - the control is unavailable, or it is blocked with a message explaining the school must retain at least one administrator - and the role is unchanged afterwards. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STF_011_N1. No counterpart existed anywhere in our register. Related but distinct from TST_STFP_TC_14, which checks an administrator can reach Remove admin rights on their own profile - this one checks what happens when doing so would leave the school with none.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): the precondition is a school with exactly one administrator. 3 July Test School 1 is shared and has several, and reducing it to one would break other suites. Unblock with a dedicated single-admin school.</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -4052,6 +4103,94 @@
         <v>24</v>
       </c>
     </row>
+    <row r="57" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="374">
   <si>
     <t>S.No.</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Search covers first name, last name and email from the single box.</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>TST_STFL_TC_3</t>
@@ -1765,7 +1768,7 @@
         <v>24</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>24</v>
@@ -1776,40 +1779,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>24</v>
@@ -1820,40 +1823,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>24</v>
@@ -1864,34 +1867,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>24</v>
@@ -1908,13 +1911,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>17</v>
@@ -1926,22 +1929,22 @@
         <v>19</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>24</v>
@@ -1952,13 +1955,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>17</v>
@@ -1967,19 +1970,19 @@
         <v>18</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>24</v>
@@ -1996,13 +1999,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>17</v>
@@ -2014,13 +2017,13 @@
         <v>19</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>21</v>
@@ -2029,7 +2032,7 @@
         <v>24</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>24</v>
@@ -2040,40 +2043,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>24</v>
@@ -2084,34 +2087,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>24</v>
@@ -2128,16 +2131,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
@@ -2146,22 +2149,22 @@
         <v>19</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>24</v>
@@ -2172,40 +2175,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>24</v>
@@ -2216,40 +2219,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>24</v>
@@ -2260,13 +2263,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -2278,22 +2281,22 @@
         <v>19</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>24</v>
@@ -2304,13 +2307,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -2322,13 +2325,13 @@
         <v>19</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>21</v>
@@ -2337,7 +2340,7 @@
         <v>24</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>24</v>
@@ -2348,13 +2351,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -2366,22 +2369,22 @@
         <v>19</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>24</v>
@@ -2392,13 +2395,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
@@ -2410,22 +2413,22 @@
         <v>19</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>24</v>
@@ -2436,40 +2439,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>24</v>
@@ -2480,31 +2483,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>21</v>
@@ -2513,7 +2516,7 @@
         <v>24</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>24</v>
@@ -2524,40 +2527,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>24</v>
@@ -2568,34 +2571,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>24</v>
@@ -2612,13 +2615,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>17</v>
@@ -2627,25 +2630,25 @@
         <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>24</v>
@@ -2656,40 +2659,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>24</v>
@@ -2700,40 +2703,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>24</v>
@@ -2744,16 +2747,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>18</v>
@@ -2762,16 +2765,16 @@
         <v>19</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>24</v>
@@ -2788,13 +2791,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>17</v>
@@ -2803,19 +2806,19 @@
         <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
@@ -2832,13 +2835,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2850,16 +2853,16 @@
         <v>19</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
@@ -2876,13 +2879,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2894,16 +2897,16 @@
         <v>19</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>24</v>
@@ -2920,13 +2923,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>17</v>
@@ -2935,19 +2938,19 @@
         <v>18</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
@@ -2964,34 +2967,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
@@ -3008,34 +3011,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>24</v>
@@ -3044,7 +3047,7 @@
         <v>25</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -3052,13 +3055,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>17</v>
@@ -3070,16 +3073,16 @@
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
@@ -3096,34 +3099,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -3140,13 +3143,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>17</v>
@@ -3155,19 +3158,19 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
@@ -3184,13 +3187,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3199,19 +3202,19 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
@@ -3228,13 +3231,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>17</v>
@@ -3243,19 +3246,19 @@
         <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>24</v>
@@ -3272,13 +3275,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>17</v>
@@ -3287,19 +3290,19 @@
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
@@ -3316,13 +3319,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>17</v>
@@ -3331,19 +3334,19 @@
         <v>18</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
@@ -3360,34 +3363,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
@@ -3404,13 +3407,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>17</v>
@@ -3419,19 +3422,19 @@
         <v>18</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
@@ -3448,13 +3451,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>17</v>
@@ -3463,19 +3466,19 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
@@ -3492,13 +3495,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>17</v>
@@ -3507,19 +3510,19 @@
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
@@ -3536,34 +3539,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
@@ -3580,13 +3583,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>17</v>
@@ -3598,16 +3601,16 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>24</v>
@@ -3624,13 +3627,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>17</v>
@@ -3639,19 +3642,19 @@
         <v>18</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
@@ -3668,34 +3671,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
@@ -3712,34 +3715,34 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>24</v>
@@ -3756,13 +3759,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -3771,19 +3774,19 @@
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
@@ -3800,34 +3803,34 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
@@ -3844,34 +3847,34 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
@@ -3888,34 +3891,34 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
@@ -3932,34 +3935,34 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
@@ -3976,34 +3979,34 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
@@ -4020,43 +4023,43 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4064,34 +4067,34 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
@@ -4108,13 +4111,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>17</v>
@@ -4123,19 +4126,19 @@
         <v>18</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>24</v>
@@ -4152,43 +4155,43 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
